--- a/Result/profitability/3362.xlsx
+++ b/Result/profitability/3362.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12875</v>
+        <v>-0.34875</v>
       </c>
       <c r="N2" t="n">
-        <v>17.44625</v>
+        <v>15.15875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.59</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.25</v>
+        <v>-0.51125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.18375</v>
+        <v>10.52</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.39375</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>10.18875</v>
+        <v>8.567499999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4675</v>
+        <v>-0.45125</v>
       </c>
       <c r="N5" t="n">
-        <v>9.03375</v>
+        <v>7.31</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3100000000000001</v>
+        <v>-0.4925</v>
       </c>
       <c r="N6" t="n">
-        <v>8.473749999999999</v>
+        <v>7.69375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2837500000000001</v>
+        <v>-0.4662500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>10.84125</v>
+        <v>9.59625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2475000000000001</v>
+        <v>-0.3575</v>
       </c>
       <c r="N8" t="n">
-        <v>14.0375</v>
+        <v>13.43875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.14</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06875000000000003</v>
+        <v>-0.06875000000000006</v>
       </c>
       <c r="N10" t="n">
         <v>19.63875</v>
@@ -1772,7 +1772,7 @@
         <v>0.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03749999999999997</v>
+        <v>0.03749999999999994</v>
       </c>
       <c r="N11" t="n">
         <v>25.2925</v>
@@ -1899,7 +1899,7 @@
         <v>-0.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06124999999999997</v>
+        <v>0.06124999999999994</v>
       </c>
       <c r="N12" t="n">
         <v>27.16625</v>
@@ -2026,7 +2026,7 @@
         <v>-1.02</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.02625000000000002</v>
+        <v>-0.02625000000000005</v>
       </c>
       <c r="N13" t="n">
         <v>25.19875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>950</v>
+      </c>
+      <c r="D75" t="n">
+        <v>871</v>
+      </c>
+      <c r="E75" t="n">
+        <v>79</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-223</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-23.52%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-236</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-198</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.23375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.789999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3653699466056445</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1300000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.08609271523178819</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.79</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6236996834011759</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
